--- a/Test2/03_Apriori/V2/Configurations/Applications.xlsx
+++ b/Test2/03_Apriori/V2/Configurations/Applications.xlsx
@@ -6,44 +6,49 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Adalimumab_Monkey_3_mpk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Atezolizumab_Human_1_mpk" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Atezolizumab_Human_3_mpk" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Atezolizumab_Human_10_mpk" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Atezolizumab_Human_15_mpk" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Atezolizumab_Human_20_mpk" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Atezolizumab_Monkey_0.5_mpk" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Atezolizumab_Monkey_5_mpk" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Atezolizumab_Monkey_20_mpk" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Avelumab_Human_1_mpk" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Avelumab_Human_3_mpk" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Avelumab_Human_10_mpk" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Avelumab_Human_20_mpk" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Avelumab_Monkey_5_mpk" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Bevacizumab_Human_15_mpk" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Bevacizumab_Monkey_4_mpk" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Bevacizumab_Monkey_5_mpk" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Golimumab_Human_0.1_mpk" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Golimumab_Human_0.3_mpk" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Golimumab_Human_1_mpk" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Golimumab_Human_3_mpk" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Golimumab_Human_6_mpk" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Golimumab_Human_10_mpk" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Golimumab_Monkey_3_mpk" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Nivolumab_Human_1_mpk" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Nivolumab_Human_3_mpk" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Nivolumab_Human_4_mpk" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Nivolumab_Human_6_mpk" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Nivolumab_Human_10_mpk" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Nivolumab_Human_20_mpk" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Nivolumab_Monkey_1_mpk" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="Nivolumab_Monkey_10_mpk" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Pembrolizumab_Human_3_mpk" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="Pembrolizumab_Monkey_0.3_mpk" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="Pembrolizumab_Monkey_3_mpk" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="Pembrolizumab_Monkey_30_mpk" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="Tocilizumab_Human_8_mpk" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="Tocilizumab_Monkey_10_mpk" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Adalimumab_Human_0.5_mpk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Adalimumab_Human_1_mpk" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Adalimumab_Human_3_mpk" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Adalimumab_Human_5_mpk" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Adalimumab_Human_10_mpk" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Adalimumab_Monkey_3_mpk" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Atezolizumab_Human_1_mpk" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Atezolizumab_Human_3_mpk" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Atezolizumab_Human_10_mpk" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Atezolizumab_Human_15_mpk" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Atezolizumab_Human_20_mpk" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Atezolizumab_Monkey_0.5_mpk" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Atezolizumab_Monkey_5_mpk" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Atezolizumab_Monkey_20_mpk" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Avelumab_Human_1_mpk" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Avelumab_Human_3_mpk" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Avelumab_Human_10_mpk" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Avelumab_Human_20_mpk" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Avelumab_Monkey_5_mpk" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Bevacizumab_Human_15_mpk" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Bevacizumab_Monkey_4_mpk" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Bevacizumab_Monkey_5_mpk" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Golimumab_Human_0.1_mpk" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Golimumab_Human_0.3_mpk" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Golimumab_Human_1_mpk" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Golimumab_Human_3_mpk" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Golimumab_Human_6_mpk" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Golimumab_Human_10_mpk" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Golimumab_Monkey_3_mpk" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Nivolumab_Human_1_mpk" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Nivolumab_Human_3_mpk" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Nivolumab_Human_4_mpk" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Nivolumab_Human_6_mpk" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Nivolumab_Human_10_mpk" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Nivolumab_Human_20_mpk" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Nivolumab_Monkey_1_mpk" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Nivolumab_Monkey_10_mpk" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Pembrolizumab_Human_3_mpk" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Pembrolizumab_Monkey_0.3_mpk" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Pembrolizumab_Monkey_3_mpk" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Pembrolizumab_Monkey_30_mpk" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="Tocilizumab_Human_8_mpk" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="Tocilizumab_Monkey_10_mpk" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
 </workbook>
 </file>
@@ -443,7 +448,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -502,7 +507,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -561,7 +566,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -620,6 +625,301 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="s">
@@ -638,7 +938,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -697,66 +997,125 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -815,125 +1174,125 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -992,7 +1351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1051,243 +1410,184 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1346,301 +1646,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -1682,6 +1687,360 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="s">
@@ -1700,66 +2059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1818,66 +2118,66 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1936,66 +2236,66 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -2054,66 +2354,125 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -2172,66 +2531,66 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -2290,7 +2649,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -2349,65 +2708,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -2449,7 +2749,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -2508,7 +2808,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -2567,7 +2867,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -2626,7 +2926,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>

--- a/Test2/03_Apriori/V2/Configurations/Applications.xlsx
+++ b/Test2/03_Apriori/V2/Configurations/Applications.xlsx
@@ -43,12 +43,13 @@
     <sheet name="Nivolumab_Human_20_mpk" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="Nivolumab_Monkey_1_mpk" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="Nivolumab_Monkey_10_mpk" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="Pembrolizumab_Human_3_mpk" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="Pembrolizumab_Monkey_0.3_mpk" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="Pembrolizumab_Monkey_3_mpk" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="Pembrolizumab_Monkey_30_mpk" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="Tocilizumab_Human_8_mpk" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="Tocilizumab_Monkey_10_mpk" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="Pembrolizumab_Human_2_mpk" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Pembrolizumab_Human_10_mpk" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Pembrolizumab_Monkey_0.3_mpk" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Pembrolizumab_Monkey_3_mpk" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="Pembrolizumab_Monkey_30_mpk" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="Tocilizumab_Human_8_mpk" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="Tocilizumab_Monkey_10_mpk" sheetId="44" state="visible" r:id="rId44"/>
   </sheets>
 </workbook>
 </file>
@@ -2277,7 +2278,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -2336,6 +2337,124 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.3</v>
       </c>
       <c r="D2" t="s">
@@ -2354,124 +2473,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -2513,6 +2514,65 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
         <v>30</v>
       </c>
       <c r="D2" t="s">
@@ -2531,65 +2591,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -2631,6 +2632,65 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="s">
